--- a/Assets/Assets/Sound/cue sheet.xlsx
+++ b/Assets/Assets/Sound/cue sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workbench\Unity Projects\GameJam2-2D-\Assets\Assets\Sound\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workbench\02_GameDev\00_Courses\00_Generation\GameJam 2\GameJam2-2D-\Assets\Assets\Sound\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98A29780-6E43-4076-BCF0-31068C108F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461BE511-8823-41A9-9C61-3C10684AF1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="3195" windowWidth="15375" windowHeight="8325" xr2:uid="{A5A50A2F-EFA3-4EB0-9DF6-8417FB7309C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{A5A50A2F-EFA3-4EB0-9DF6-8417FB7309C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>nombre de sonido</t>
   </si>
@@ -69,14 +69,31 @@
   </si>
   <si>
     <t>Se puede usar circunstancial para cuando aparece un enemigo</t>
+  </si>
+  <si>
+    <t>cave</t>
+  </si>
+  <si>
+    <t>ambience</t>
+  </si>
+  <si>
+    <t>sonido de cueva</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -104,8 +121,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924C701D-AA08-44E9-8C5B-8C5707A61D5E}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -490,6 +508,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Assets/Sound/cue sheet.xlsx
+++ b/Assets/Assets/Sound/cue sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workbench\02_GameDev\00_Courses\00_Generation\GameJam 2\GameJam2-2D-\Assets\Assets\Sound\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461BE511-8823-41A9-9C61-3C10684AF1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC915D5E-0DAD-4913-AEDF-C823633B2E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{A5A50A2F-EFA3-4EB0-9DF6-8417FB7309C7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>nombre de sonido</t>
   </si>
@@ -78,6 +78,27 @@
   </si>
   <si>
     <t>sonido de cueva</t>
+  </si>
+  <si>
+    <t>deliver cat</t>
+  </si>
+  <si>
+    <t>player</t>
+  </si>
+  <si>
+    <t>aumentar la velocidad</t>
+  </si>
+  <si>
+    <t>footsteps01</t>
+  </si>
+  <si>
+    <t>pisadas con eco de zapato</t>
+  </si>
+  <si>
+    <t>footsteps02</t>
+  </si>
+  <si>
+    <t>pisadas metalicas</t>
   </si>
 </sst>
 </file>
@@ -458,13 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924C701D-AA08-44E9-8C5B-8C5707A61D5E}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,7 +496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -486,7 +507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -497,7 +518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -508,7 +529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -519,8 +540,41 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
